--- a/data/dividends_info_20260305.xlsx
+++ b/data/dividends_info_20260305.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>53.20000076293945</v>
+        <v>51.90000152587891</v>
       </c>
       <c r="I2" t="n">
-        <v>1.315789454814517</v>
+        <v>1.348747551868489</v>
       </c>
       <c r="J2" t="n">
         <v>347</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>22.27000045776367</v>
+        <v>21.88999938964844</v>
       </c>
       <c r="I3" t="n">
-        <v>3.816793814674919</v>
+        <v>3.883051730014924</v>
       </c>
       <c r="J3" t="n">
         <v>109</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.283999919891357</v>
+        <v>4.070000171661377</v>
       </c>
       <c r="I4" t="n">
-        <v>2.334267083799012</v>
+        <v>2.457002353372873</v>
       </c>
       <c r="J4" t="n">
         <v>74</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>76.22000122070312</v>
+        <v>75.40000152587891</v>
       </c>
       <c r="I5" t="n">
-        <v>1.364471245531169</v>
+        <v>1.379310316914317</v>
       </c>
       <c r="J5" t="n">
         <v>74</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>53.20000076293945</v>
+        <v>51.90000152587891</v>
       </c>
       <c r="I6" t="n">
-        <v>4.135338286559912</v>
+        <v>4.238920877300965</v>
       </c>
       <c r="J6" t="n">
         <v>74</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19.46500015258789</v>
+        <v>19.14500045776367</v>
       </c>
       <c r="I7" t="n">
-        <v>4.058566626288821</v>
+        <v>4.126403662109287</v>
       </c>
       <c r="J7" t="n">
         <v>74</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.421999931335449</v>
+        <v>5.315000057220459</v>
       </c>
       <c r="I8" t="n">
-        <v>3.504242021508153</v>
+        <v>3.574788296415611</v>
       </c>
       <c r="J8" t="n">
         <v>74</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10.48999977111816</v>
+        <v>10.56999969482422</v>
       </c>
       <c r="I9" t="n">
-        <v>4.118207906823926</v>
+        <v>4.087038907026044</v>
       </c>
       <c r="J9" t="n">
         <v>74</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>24.29999923706055</v>
+        <v>24.63999938964844</v>
       </c>
       <c r="I10" t="n">
-        <v>1.810699645327333</v>
+        <v>1.785714329947789</v>
       </c>
       <c r="J10" t="n">
         <v>74</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>54.08000183105469</v>
+        <v>54.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.588757308798887</v>
+        <v>2.568807339449541</v>
       </c>
       <c r="J11" t="n">
         <v>74</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>22.95999908447266</v>
+        <v>22.68000030517578</v>
       </c>
       <c r="I12" t="n">
-        <v>2.613240522321131</v>
+        <v>2.645502609905497</v>
       </c>
       <c r="J12" t="n">
         <v>74</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8.760000228881836</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I13" t="n">
-        <v>5.827625418511689</v>
+        <v>5.93604624832303</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I14" t="n">
-        <v>3.947368421052631</v>
+        <v>3.968254048347555</v>
       </c>
       <c r="J14" t="n">
         <v>60</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3.984999895095825</v>
+        <v>3.940000057220459</v>
       </c>
       <c r="I15" t="n">
-        <v>3.764115531962719</v>
+        <v>3.807106543694319</v>
       </c>
       <c r="J15" t="n">
         <v>60</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2.214999914169312</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I16" t="n">
-        <v>2.93453735976224</v>
+        <v>2.941176419820373</v>
       </c>
       <c r="J16" t="n">
         <v>53</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6.864999771118164</v>
+        <v>6.75</v>
       </c>
       <c r="I17" t="n">
-        <v>7.283321437293515</v>
+        <v>7.407407407407407</v>
       </c>
       <c r="J17" t="n">
         <v>46</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>11.90499973297119</v>
+        <v>11.68000030517578</v>
       </c>
       <c r="I18" t="n">
-        <v>4.535909383554682</v>
+        <v>4.623287550435327</v>
       </c>
       <c r="J18" t="n">
         <v>46</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>312.7999877929688</v>
+        <v>308.1000061035156</v>
       </c>
       <c r="I19" t="n">
-        <v>1.155690582185266</v>
+        <v>1.173320327291857</v>
       </c>
       <c r="J19" t="n">
         <v>46</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>26.20000076293945</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="I20" t="n">
-        <v>5.190839543500142</v>
+        <v>5.018450113860267</v>
       </c>
       <c r="J20" t="n">
         <v>46</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>14</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="I21" t="n">
-        <v>4.178571428571428</v>
+        <v>4.295154221111702</v>
       </c>
       <c r="J21" t="n">
         <v>46</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>16.82999992370605</v>
+        <v>16.06500053405762</v>
       </c>
       <c r="I22" t="n">
-        <v>3.74331552499063</v>
+        <v>3.921568497084126</v>
       </c>
       <c r="J22" t="n">
         <v>46</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>102.1999969482422</v>
+        <v>98.59999847412109</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8806262493880433</v>
+        <v>0.9127789187909746</v>
       </c>
       <c r="J23" t="n">
         <v>46</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>68.79000091552734</v>
+        <v>66.93000030517578</v>
       </c>
       <c r="I24" t="n">
-        <v>2.501526351356072</v>
+        <v>2.571044362996856</v>
       </c>
       <c r="J24" t="n">
         <v>46</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>23.60000038146973</v>
+        <v>25.10000038146973</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5932203293942544</v>
+        <v>0.5577689158258186</v>
       </c>
       <c r="J25" t="n">
         <v>39</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.539999961853027</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="I26" t="n">
-        <v>3.896103992613359</v>
+        <v>3.846153987229934</v>
       </c>
       <c r="J26" t="n">
         <v>39</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>19.95999908447266</v>
+        <v>20.21999931335449</v>
       </c>
       <c r="I27" t="n">
-        <v>1.302605270168875</v>
+        <v>1.285855632192235</v>
       </c>
       <c r="J27" t="n">
         <v>18</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>27.7450008392334</v>
+        <v>28.59499931335449</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3243827618586106</v>
+        <v>0.3147403467779348</v>
       </c>
       <c r="J28" t="n">
         <v>18</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>53.20000076293945</v>
+        <v>51.90000152587891</v>
       </c>
       <c r="I29" t="n">
-        <v>1.221804493756337</v>
+        <v>1.252408441020739</v>
       </c>
       <c r="J29" t="n">
         <v>-10</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.509999990463257</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I30" t="n">
-        <v>3.973509958870426</v>
+        <v>4.026845611810072</v>
       </c>
       <c r="J30" t="n">
         <v>-24</v>
@@ -1862,7 +1862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C251"/>
+  <dimension ref="A1:C386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2191,7 +2191,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2242,7 +2242,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2276,7 +2276,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Banca Popolare di Sondrio S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2293,7 +2293,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Banca Popolare di Sondrio S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2344,7 +2344,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2371,14 +2371,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2388,14 +2388,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2412,7 +2412,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2422,14 +2422,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2446,7 +2446,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2480,7 +2480,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2497,7 +2497,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2514,7 +2514,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2524,14 +2524,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2541,14 +2541,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2565,12 +2565,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2582,29 +2582,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2616,46 +2616,46 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2684,7 +2684,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2718,7 +2718,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2752,7 +2752,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2769,7 +2769,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2779,14 +2779,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2796,14 +2796,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2813,14 +2813,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2837,7 +2837,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2864,14 +2864,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2888,7 +2888,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2898,14 +2898,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2915,14 +2915,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2932,19 +2932,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2956,12 +2956,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2973,29 +2973,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3007,46 +3007,46 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3058,63 +3058,63 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3126,12 +3126,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3143,12 +3143,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3160,12 +3160,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3177,46 +3177,46 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3228,12 +3228,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3245,12 +3245,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3262,29 +3262,29 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3296,131 +3296,131 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3432,29 +3432,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3466,29 +3466,29 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3500,12 +3500,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3517,12 +3517,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3534,46 +3534,46 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3585,29 +3585,29 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3619,29 +3619,29 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3653,29 +3653,29 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3687,63 +3687,63 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3772,63 +3772,63 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3840,12 +3840,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3857,12 +3857,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3874,29 +3874,29 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3908,29 +3908,29 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3942,46 +3942,46 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3993,12 +3993,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4010,29 +4010,29 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4044,12 +4044,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4061,12 +4061,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4078,29 +4078,29 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4112,12 +4112,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4129,29 +4129,29 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4163,12 +4163,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4180,12 +4180,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4197,12 +4197,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4214,12 +4214,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4231,29 +4231,29 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4265,63 +4265,63 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4333,29 +4333,29 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4367,46 +4367,46 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4418,12 +4418,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4435,12 +4435,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4452,29 +4452,29 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4486,12 +4486,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4503,46 +4503,46 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4554,29 +4554,29 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4588,12 +4588,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4605,12 +4605,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4622,12 +4622,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4656,12 +4656,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4673,29 +4673,29 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4707,29 +4707,29 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4741,12 +4741,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4758,29 +4758,29 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4792,12 +4792,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4809,12 +4809,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4826,12 +4826,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4843,12 +4843,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4860,12 +4860,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4877,12 +4877,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4894,12 +4894,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4911,12 +4911,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4928,12 +4928,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4945,12 +4945,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4962,12 +4962,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4979,12 +4979,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4996,12 +4996,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5013,46 +5013,46 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5064,12 +5064,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5081,29 +5081,29 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5115,12 +5115,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5132,29 +5132,29 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5166,12 +5166,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5183,12 +5183,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5200,29 +5200,29 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5234,29 +5234,29 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5268,12 +5268,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5285,12 +5285,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5302,12 +5302,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5319,12 +5319,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5336,12 +5336,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5353,12 +5353,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5370,12 +5370,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5387,12 +5387,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5404,29 +5404,29 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5438,29 +5438,29 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5472,12 +5472,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5489,46 +5489,46 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5540,12 +5540,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5557,12 +5557,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5574,12 +5574,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5591,12 +5591,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5608,29 +5608,29 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5642,12 +5642,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5659,12 +5659,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5676,12 +5676,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5693,12 +5693,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5710,46 +5710,46 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5761,29 +5761,29 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5795,29 +5795,29 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5829,29 +5829,29 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5863,12 +5863,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5880,12 +5880,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5897,29 +5897,29 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5931,12 +5931,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5948,12 +5948,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5965,29 +5965,29 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5999,29 +5999,29 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6033,46 +6033,46 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6084,12 +6084,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6101,12 +6101,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -6118,17 +6118,2312 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
+          <t>Racing Force S.p.A.</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>RES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Pirelli &amp; C. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>KME Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Intred S.p.A.</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>MARZOCCHI POMPE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Magis S.p.A.</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ELES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Yakkyo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>EDILIZIACROBATICA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Vimi Fasteners S.p.A.</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>VINEXT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Lemon Sistemi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>UCapital24 S.p.A.</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>TradeLab S.p.A.</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Telmes S.p.A.</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Smart Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SOSTRAVEL.COM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>YOLO GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Italian Wine Brands S.p.A.</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>SBE-Varvit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SIAV S.p.A.</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Arterra Bioscience S.p.A.</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Bellini Nautica S.p.A.</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CIRCLE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Copernico SIM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>DEODATO.GALLERY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>DESTINATION ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ESAUTOMOTION S.p.A.</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Energy S.p.A.</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SOGES GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Metriks AI S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>OSAI Automation System S.p.A.</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>PHILOGEN S.p.A.</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>PREMIA FINANCE S.P.A</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Riba Mundo Tecnologia S.A.</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>International Care Company S.p.A.</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Haiki+ S.p.A.</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>HEALTH ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>AATECH S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>GREEN OLEO S.p.A</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>INNOVATEC S.p.A.</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>KALEON S.P.A.</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Leone Film Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Litix S.p.A.</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>MIT SIM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Gentili Mosconi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>MONDO TV FRANCE</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>NEWPRINCES</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Estrima S.p.A.</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>FRANCHETTI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Farmacosmo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>First Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>GPI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Markbass S.p.A.</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Pasquarelli Auto S.p.A.</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ABC Company S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ACQUAZZURRA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Ambromobiliare S.p.A.</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>BFF Bank S.P.A.</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>COFLE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Novamarine S.p.A.</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>OLIDATA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>OSAI Automation System S.p.A.</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>OSAI Automation System S.p.A.</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Otofarma S.p.A.</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>PLANETEL S.p.A.</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>PROMOTICA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Annual Preliminary Results</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Datrix S.p.A.</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Emma Villas S.p.A.</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>RedFish LongTerm Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>A.B.P. Nocivelli S.p.A.</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>E-Globe S.p.A.</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>EDISON S.p.A.</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>EUKEDOS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>EdgeLab S.p.A.</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>ILPRA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Redelfi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Energy Time S.p.A.</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ErreDue S.p.A.</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>iVision Tech S.p.A.</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>doxee S.p.A.</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Tenax International S.p.A.</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>T.P.S. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Energy S.p.A.</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>WEBSOLUTE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>ROSETTI MARINO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Reti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Execus S.p.A.</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>DigiTouch S.p.A.</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>DigiTouch S.p.A.</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Dedem S.p.A.</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Vivenda Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Vantea Smart S.p.A.</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Valica S.p.A.</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>VNE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
           <t>VALTECNE S.p.A.</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Unicredit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Tecno S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Solid World Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Società Editoriale il Fatto S.p.A.</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Seri Industrial S.p.A.</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Reway Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>GEL S.p.A.</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Ferretti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Pozzi Milano S.p.A.</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>OPS Retail S.p.A.</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>OPS ECOM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>NEUROSOFT</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>MONDO TV S.p.A.</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Gismondi 1754 S.p.A.</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>CleanBnB S.p.A.</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>CALEFFI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>BUZZI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>A.B.P. Nocivelli S.p.A.</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Lucisano Media Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Com.Tel S.p.A.</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>INWIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Digital Value S.p.A.</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>INWIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Reti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -6143,146 +8438,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Italgas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005211237</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>10.48999977111816</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4.118207906823926</v>
-      </c>
-      <c r="I2" t="n">
-        <v>74</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0004931058</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-04-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4.178571428571428</v>
-      </c>
-      <c r="I3" t="n">
-        <v>46</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6293,9 +8451,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACEA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UNIDATA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UNIDATA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>